--- a/_000_Global_Define.xlsx
+++ b/_000_Global_Define.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\UnityPortfolioProjectTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06219B5-23D7-44BA-A79F-190136650293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82430DF0-8367-4C7D-A999-05621958B77F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="11477" yWindow="4123" windowWidth="24686" windowHeight="13054" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -223,9 +223,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0000000"/>
-  </numFmts>
   <fonts count="4">
     <font>
       <sz val="11"/>
@@ -297,28 +294,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -328,61 +307,28 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -722,494 +668,381 @@
   <dimension ref="A2:H53"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001"/>
   <cols>
-    <col min="1" max="1" width="15.640625" style="6" customWidth="1"/>
-    <col min="2" max="3" width="15.640625" style="9" customWidth="1"/>
-    <col min="4" max="19" width="15.640625" customWidth="1"/>
-    <col min="20" max="37" width="12.5703125" customWidth="1"/>
+    <col min="1" max="19" width="15.640625" style="3" customWidth="1"/>
+    <col min="20" max="37" width="12.5703125" style="3" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" s="1" customFormat="1">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:8" s="10" customFormat="1">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="2" customFormat="1">
-      <c r="A3" s="13" t="s">
+    <row r="3" spans="1:8" s="1" customFormat="1">
+      <c r="A3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="3" customFormat="1">
-      <c r="A4" s="14" t="s">
+    <row r="4" spans="1:8" s="2" customFormat="1">
+      <c r="A4" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="2" customFormat="1">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:8" s="1" customFormat="1">
+      <c r="A5" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="13" t="s">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13" t="s">
+      <c r="D5" s="5"/>
+      <c r="E5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13" t="s">
+      <c r="F5" s="5"/>
+      <c r="G5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="3" customFormat="1">
-      <c r="A6" s="16"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14" t="s">
+    <row r="6" spans="1:8" s="2" customFormat="1">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14" t="s">
+      <c r="F6" s="6"/>
+      <c r="G6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="2" customFormat="1">
-      <c r="A7" s="18"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13" t="s">
+    <row r="7" spans="1:8" s="1" customFormat="1">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13" t="s">
+      <c r="F7" s="5"/>
+      <c r="G7" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="3" customFormat="1">
-      <c r="A8" s="16"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14" t="s">
+    <row r="8" spans="1:8" s="2" customFormat="1">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14" t="s">
+      <c r="F8" s="6"/>
+      <c r="G8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="2" customFormat="1">
-      <c r="A9" s="18"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13" t="s">
+    <row r="9" spans="1:8" s="1" customFormat="1">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13" t="s">
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="3" customFormat="1">
-      <c r="A10" s="16"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14" t="s">
+    <row r="10" spans="1:8" s="2" customFormat="1">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-    </row>
-    <row r="11" spans="1:8" s="2" customFormat="1">
-      <c r="A11" s="18"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13" t="s">
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+    </row>
+    <row r="11" spans="1:8" s="1" customFormat="1">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-    </row>
-    <row r="12" spans="1:8" s="3" customFormat="1">
-      <c r="A12" s="16"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14" t="s">
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="1:8" s="2" customFormat="1">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-    </row>
-    <row r="13" spans="1:8" s="2" customFormat="1">
-      <c r="A13" s="18"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13" t="s">
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+    </row>
+    <row r="13" spans="1:8" s="1" customFormat="1">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-    </row>
-    <row r="14" spans="1:8" s="3" customFormat="1">
-      <c r="A14" s="16"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14" t="s">
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="1:8" s="2" customFormat="1">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-    </row>
-    <row r="15" spans="1:8" s="2" customFormat="1">
-      <c r="A15" s="18"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13" t="s">
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" spans="1:8" s="1" customFormat="1">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-    </row>
-    <row r="16" spans="1:8" s="3" customFormat="1">
-      <c r="A16" s="16"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14" t="s">
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:8" s="2" customFormat="1">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-    </row>
-    <row r="17" spans="1:8" s="2" customFormat="1">
-      <c r="A17" s="18"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13" t="s">
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="1:8" s="1" customFormat="1">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-    </row>
-    <row r="18" spans="1:8" s="3" customFormat="1">
-      <c r="A18" s="16"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14" t="s">
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" s="2" customFormat="1">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-    </row>
-    <row r="19" spans="1:8" s="2" customFormat="1">
-      <c r="A19" s="18"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13" t="s">
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+    </row>
+    <row r="19" spans="1:8" s="1" customFormat="1">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-    </row>
-    <row r="20" spans="1:8" s="3" customFormat="1">
-      <c r="A20" s="16"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-    </row>
-    <row r="21" spans="1:8" s="2" customFormat="1">
-      <c r="A21" s="18"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-    </row>
-    <row r="22" spans="1:8" s="3" customFormat="1">
-      <c r="A22" s="16"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-    </row>
-    <row r="23" spans="1:8" s="2" customFormat="1">
-      <c r="A23" s="20"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-    </row>
-    <row r="24" spans="1:8" s="3" customFormat="1">
-      <c r="A24" s="23"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-    </row>
-    <row r="25" spans="1:8" s="2" customFormat="1">
-      <c r="A25" s="26"/>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-    </row>
-    <row r="26" spans="1:8" s="3" customFormat="1">
-      <c r="A26" s="5"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-    </row>
-    <row r="27" spans="1:8" s="2" customFormat="1">
-      <c r="A27" s="4"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-    </row>
-    <row r="28" spans="1:8" s="3" customFormat="1">
-      <c r="A28" s="5"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-    </row>
-    <row r="29" spans="1:8" s="2" customFormat="1">
-      <c r="A29" s="4"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-    </row>
-    <row r="30" spans="1:8" s="3" customFormat="1">
-      <c r="A30" s="5"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-    </row>
-    <row r="31" spans="1:8" s="2" customFormat="1">
-      <c r="A31" s="4"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-    </row>
-    <row r="32" spans="1:8" s="3" customFormat="1">
-      <c r="A32" s="5"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-    </row>
-    <row r="33" spans="1:3" s="2" customFormat="1">
-      <c r="A33" s="4"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-    </row>
-    <row r="34" spans="1:3" s="3" customFormat="1">
-      <c r="A34" s="5"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-    </row>
-    <row r="35" spans="1:3" s="2" customFormat="1">
-      <c r="A35" s="4"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-    </row>
-    <row r="36" spans="1:3" s="3" customFormat="1">
-      <c r="A36" s="5"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-    </row>
-    <row r="37" spans="1:3" s="2" customFormat="1">
-      <c r="A37" s="4"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-    </row>
-    <row r="38" spans="1:3" s="3" customFormat="1">
-      <c r="A38" s="5"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-    </row>
-    <row r="39" spans="1:3" s="2" customFormat="1">
-      <c r="A39" s="4"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-    </row>
-    <row r="40" spans="1:3" s="3" customFormat="1">
-      <c r="A40" s="5"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-    </row>
-    <row r="41" spans="1:3" s="2" customFormat="1">
-      <c r="A41" s="4"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-    </row>
-    <row r="42" spans="1:3" s="3" customFormat="1">
-      <c r="A42" s="5"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-    </row>
-    <row r="43" spans="1:3" s="2" customFormat="1">
-      <c r="A43" s="4"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-    </row>
-    <row r="44" spans="1:3" s="3" customFormat="1">
-      <c r="A44" s="5"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-    </row>
-    <row r="45" spans="1:3" s="2" customFormat="1">
-      <c r="A45" s="4"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-    </row>
-    <row r="46" spans="1:3" s="3" customFormat="1">
-      <c r="A46" s="5"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-    </row>
-    <row r="47" spans="1:3" s="2" customFormat="1">
-      <c r="A47" s="4"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-    </row>
-    <row r="48" spans="1:3" s="3" customFormat="1">
-      <c r="A48" s="5"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-    </row>
-    <row r="49" spans="1:3" s="2" customFormat="1">
-      <c r="A49" s="4"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-    </row>
-    <row r="50" spans="1:3" s="3" customFormat="1">
-      <c r="A50" s="5"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-    </row>
-    <row r="51" spans="1:3" s="2" customFormat="1">
-      <c r="A51" s="4"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-    </row>
-    <row r="52" spans="1:3" s="3" customFormat="1">
-      <c r="A52" s="5"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-    </row>
-    <row r="53" spans="1:3" s="2" customFormat="1">
-      <c r="A53" s="4"/>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
-    </row>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" s="2" customFormat="1">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+    </row>
+    <row r="21" spans="1:8" s="1" customFormat="1">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" s="2" customFormat="1">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+    </row>
+    <row r="23" spans="1:8" s="1" customFormat="1">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+    </row>
+    <row r="24" spans="1:8" s="2" customFormat="1">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" spans="1:8" s="1" customFormat="1">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+    </row>
+    <row r="26" spans="1:8" s="2" customFormat="1"/>
+    <row r="27" spans="1:8" s="1" customFormat="1"/>
+    <row r="28" spans="1:8" s="2" customFormat="1"/>
+    <row r="29" spans="1:8" s="1" customFormat="1"/>
+    <row r="30" spans="1:8" s="2" customFormat="1"/>
+    <row r="31" spans="1:8" s="1" customFormat="1"/>
+    <row r="32" spans="1:8" s="2" customFormat="1"/>
+    <row r="33" s="1" customFormat="1"/>
+    <row r="34" s="2" customFormat="1"/>
+    <row r="35" s="1" customFormat="1"/>
+    <row r="36" s="2" customFormat="1"/>
+    <row r="37" s="1" customFormat="1"/>
+    <row r="38" s="2" customFormat="1"/>
+    <row r="39" s="1" customFormat="1"/>
+    <row r="40" s="2" customFormat="1"/>
+    <row r="41" s="1" customFormat="1"/>
+    <row r="42" s="2" customFormat="1"/>
+    <row r="43" s="1" customFormat="1"/>
+    <row r="44" s="2" customFormat="1"/>
+    <row r="45" s="1" customFormat="1"/>
+    <row r="46" s="2" customFormat="1"/>
+    <row r="47" s="1" customFormat="1"/>
+    <row r="48" s="2" customFormat="1"/>
+    <row r="49" s="1" customFormat="1"/>
+    <row r="50" s="2" customFormat="1"/>
+    <row r="51" s="1" customFormat="1"/>
+    <row r="52" s="2" customFormat="1"/>
+    <row r="53" s="1" customFormat="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_000_Global_Define.xlsx
+++ b/_000_Global_Define.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\UnityPortfolioProjectTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82430DF0-8367-4C7D-A999-05621958B77F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB355AE-23D4-4E70-8C52-62A969688DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11477" yWindow="4123" windowWidth="24686" windowHeight="13054" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
   <si>
     <t>Gold</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -72,15 +72,6 @@
   <si>
     <t>CharacterState</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack,</t>
-  </si>
-  <si>
-    <t>Die,</t>
-  </si>
-  <si>
-    <t>Ceremony,</t>
   </si>
   <si>
     <t>Idle</t>
@@ -701,74 +692,74 @@
     </row>
     <row r="3" spans="1:8" s="1" customFormat="1">
       <c r="A3" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="2" customFormat="1">
       <c r="A4" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="1" customFormat="1">
       <c r="A5" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="2" customFormat="1">
@@ -777,14 +768,14 @@
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
       <c r="E6" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="1" customFormat="1">
@@ -793,14 +784,14 @@
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="2" customFormat="1">
@@ -809,14 +800,14 @@
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="1" customFormat="1">
@@ -825,14 +816,14 @@
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="2" customFormat="1">
@@ -841,7 +832,7 @@
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
@@ -853,7 +844,7 @@
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
@@ -865,7 +856,7 @@
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
@@ -877,7 +868,7 @@
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -889,7 +880,7 @@
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
@@ -901,7 +892,7 @@
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
@@ -913,7 +904,7 @@
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
@@ -925,7 +916,7 @@
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -937,7 +928,7 @@
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
@@ -949,7 +940,7 @@
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>

--- a/_000_Global_Define.xlsx
+++ b/_000_Global_Define.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\UnityPortfolioProjectTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB355AE-23D4-4E70-8C52-62A969688DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA7EB8F-907B-4CFC-B58F-B2F9F0F961B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="32811" yWindow="4723" windowWidth="22149" windowHeight="13200" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="44">
   <si>
     <t>Gold</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -198,15 +198,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> Korean</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> English</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> Japanese</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Korean</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>English</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Japanese</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -692,7 +696,7 @@
     </row>
     <row r="3" spans="1:8" s="1" customFormat="1">
       <c r="A3" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>36</v>
@@ -718,7 +722,7 @@
     </row>
     <row r="4" spans="1:8" s="2" customFormat="1">
       <c r="A4" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>39</v>
@@ -744,7 +748,7 @@
     </row>
     <row r="5" spans="1:8" s="1" customFormat="1">
       <c r="A5" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5" t="s">

--- a/_000_Global_Define.xlsx
+++ b/_000_Global_Define.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\UnityPortfolioProjectTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA7EB8F-907B-4CFC-B58F-B2F9F0F961B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9574C73-D6C8-4823-B6F7-420129F5376F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32811" yWindow="4723" windowWidth="22149" windowHeight="13200" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
   <si>
     <t>Gold</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -174,14 +174,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> Stage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Main</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Logo</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -198,10 +190,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> Japanese</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Korean</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -211,6 +199,10 @@
   </si>
   <si>
     <t>Japanese</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -696,16 +688,16 @@
     </row>
     <row r="3" spans="1:8" s="1" customFormat="1">
       <c r="A3" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>13</v>
@@ -722,16 +714,16 @@
     </row>
     <row r="4" spans="1:8" s="2" customFormat="1">
       <c r="A4" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>14</v>
@@ -748,11 +740,11 @@
     </row>
     <row r="5" spans="1:8" s="1" customFormat="1">
       <c r="A5" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
